--- a/exports/tonghop_CS101.xlsx
+++ b/exports/tonghop_CS101.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -477,7 +477,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -486,12 +486,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SV002</t>
+          <t>T111</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tran Thi B</t>
+          <t>Nguyễn Quang Thông</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -501,37 +501,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
         <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SV003</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Le Van C</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
